--- a/outputs/reports/seguimiento.xlsx
+++ b/outputs/reports/seguimiento.xlsx
@@ -451,10 +451,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B2" t="n">
-        <v>9995761.349656502</v>
+        <v>9995776.120101618</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
@@ -512,7 +512,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -520,21 +520,21 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28141.90361056569</v>
+        <v>28872.83309006957</v>
       </c>
       <c r="D2" t="n">
-        <v>27.15999984741211</v>
+        <v>27.20199966430664</v>
       </c>
       <c r="E2" t="n">
-        <v>764334.0977688503</v>
+        <v>785398.7960236541</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07646582096471483</v>
+        <v>0.07857306792258065</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -542,21 +542,21 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5994.755094539674</v>
+        <v>6013.643492826332</v>
       </c>
       <c r="D3" t="n">
-        <v>429.4100036621094</v>
+        <v>429.1600036621094</v>
       </c>
       <c r="E3" t="n">
-        <v>2574207.80709973</v>
+        <v>2580815.263403969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2575299386462634</v>
+        <v>0.2581905829417208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -564,21 +564,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47119.18011910182</v>
+        <v>46449.30354263495</v>
       </c>
       <c r="D4" t="n">
-        <v>95.26000213623047</v>
+        <v>95.00499725341797</v>
       </c>
       <c r="E4" t="n">
-        <v>4488573.198803068</v>
+        <v>4412915.95549121</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4490476554802216</v>
+        <v>0.4414780705839126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -586,21 +586,21 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23928.59816401738</v>
+        <v>23253.48846347147</v>
       </c>
       <c r="D5" t="n">
         <v>53.9900016784668</v>
       </c>
       <c r="E5" t="n">
-        <v>1291905.055038656</v>
+        <v>1255455.881173033</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1292452880623297</v>
+        <v>0.1255986394741572</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -608,21 +608,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12788.98552937062</v>
+        <v>12262.12970237731</v>
       </c>
       <c r="D6" t="n">
         <v>127.4899978637695</v>
       </c>
       <c r="E6" t="n">
-        <v>1630467.73781924</v>
+        <v>1563298.889561348</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1631159129139542</v>
+        <v>0.1563959487265362</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -630,21 +630,21 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10188.92949297154</v>
+        <v>10017.11348905571</v>
       </c>
       <c r="D7" t="n">
-        <v>74.16999816894531</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="E7" t="n">
-        <v>755712.8818372117</v>
+        <v>736558.3426223443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07560333379339647</v>
+        <v>0.07368695874861755</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1151.693324867209</v>
+        <v>1257.039144290156</v>
       </c>
       <c r="D8" t="n">
-        <v>339.6099853515625</v>
+        <v>341.7699890136719</v>
       </c>
       <c r="E8" t="n">
-        <v>391126.5531876452</v>
+        <v>429618.2545338022</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03912924083577545</v>
+        <v>0.04297997968060079</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -674,21 +674,21 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5757.4623890181</v>
+        <v>5202.762789846001</v>
       </c>
       <c r="D9" t="n">
-        <v>59.25</v>
+        <v>59.17499923706055</v>
       </c>
       <c r="E9" t="n">
-        <v>341129.6465493224</v>
+        <v>307873.4841197442</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03412743007925505</v>
+        <v>0.0308003581133242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -696,21 +696,21 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19662.5278108136</v>
+        <v>21247.56860795812</v>
       </c>
       <c r="D10" t="n">
-        <v>49.52999877929688</v>
+        <v>49.91500091552734</v>
       </c>
       <c r="E10" t="n">
-        <v>973884.9784674885</v>
+        <v>1060572.40651896</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0974297949301236</v>
+        <v>0.1061020568864219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -718,21 +718,21 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16502.46934152341</v>
+        <v>15787.5483185947</v>
       </c>
       <c r="D11" t="n">
-        <v>163.7700042724609</v>
+        <v>163.6900024414062</v>
       </c>
       <c r="E11" t="n">
-        <v>2702609.474567445</v>
+        <v>2584263.822814585</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2703755501986168</v>
+        <v>0.2585355846073424</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -740,21 +740,21 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6739.401903224707</v>
+        <v>7131.185015196284</v>
       </c>
       <c r="D12" t="n">
-        <v>135.9900054931641</v>
+        <v>136.5599975585938</v>
       </c>
       <c r="E12" t="n">
-        <v>916491.3018401682</v>
+        <v>973834.6082650848</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09168799351853903</v>
+        <v>0.09742461181245271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -762,21 +762,21 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3267.606407570322</v>
+        <v>4796.472816393295</v>
       </c>
       <c r="D13" t="n">
-        <v>81.88999938964844</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="E13" t="n">
-        <v>267584.286721545</v>
+        <v>394893.615756264</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02676977544394258</v>
+        <v>0.03950604845602019</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51606.02126301121</v>
+        <v>51793.48121020371</v>
       </c>
       <c r="D14" t="n">
-        <v>46.34000015258789</v>
+        <v>46.41500091552734</v>
       </c>
       <c r="E14" t="n">
-        <v>2391423.033202393</v>
+        <v>2403994.477789953</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2392437103637507</v>
+        <v>0.2405010325266783</v>
       </c>
     </row>
   </sheetData>
@@ -849,7 +849,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28141.90361056569</v>
+        <v>28872.83309006957</v>
       </c>
       <c r="D2" t="n">
-        <v>27.15999984741211</v>
+        <v>27.20199966430664</v>
       </c>
       <c r="E2" t="n">
-        <v>764334.0977688503</v>
+        <v>785398.7960236541</v>
       </c>
       <c r="F2" t="n">
-        <v>232.2085205726655</v>
+        <v>238.6080812259662</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5994.755094539674</v>
+        <v>6013.643492826332</v>
       </c>
       <c r="D3" t="n">
-        <v>429.4100036621094</v>
+        <v>429.1600036621094</v>
       </c>
       <c r="E3" t="n">
-        <v>2574207.80709973</v>
+        <v>2580815.263403969</v>
       </c>
       <c r="F3" t="n">
-        <v>457.2591069829322</v>
+        <v>458.4327960537104</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47119.18011910182</v>
+        <v>46449.30354263495</v>
       </c>
       <c r="D4" t="n">
-        <v>95.26000213623047</v>
+        <v>95.00499725341797</v>
       </c>
       <c r="E4" t="n">
-        <v>4488573.198803068</v>
+        <v>4412915.95549121</v>
       </c>
       <c r="F4" t="n">
-        <v>682.4830663048077</v>
+        <v>670.979458116483</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23928.59816401738</v>
+        <v>23253.48846347147</v>
       </c>
       <c r="D5" t="n">
         <v>53.9900016784668</v>
       </c>
       <c r="E5" t="n">
-        <v>1291905.055038656</v>
+        <v>1255455.881173033</v>
       </c>
       <c r="F5" t="n">
-        <v>634.4171072828879</v>
+        <v>616.5179750235226</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -965,16 +965,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12788.98552937062</v>
+        <v>12262.12970237731</v>
       </c>
       <c r="D6" t="n">
         <v>127.4899978637695</v>
       </c>
       <c r="E6" t="n">
-        <v>1630467.73781924</v>
+        <v>1563298.889561348</v>
       </c>
       <c r="F6" t="n">
-        <v>312.4612068079413</v>
+        <v>299.5890358966471</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10188.92949297154</v>
+        <v>10017.11348905571</v>
       </c>
       <c r="D7" t="n">
-        <v>74.16999816894531</v>
+        <v>73.52999877929688</v>
       </c>
       <c r="E7" t="n">
-        <v>755712.8818372117</v>
+        <v>736558.3426223443</v>
       </c>
       <c r="F7" t="n">
-        <v>452.7679917564831</v>
+        <v>441.2919901402972</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1151.693324867209</v>
+        <v>1257.039144290156</v>
       </c>
       <c r="D8" t="n">
-        <v>339.6099853515625</v>
+        <v>341.7699890136719</v>
       </c>
       <c r="E8" t="n">
-        <v>391126.5531876452</v>
+        <v>429618.2545338022</v>
       </c>
       <c r="F8" t="n">
-        <v>71.20967365300224</v>
+        <v>78.21758827518762</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5757.4623890181</v>
+        <v>5202.762789846001</v>
       </c>
       <c r="D9" t="n">
-        <v>59.25</v>
+        <v>59.17499923706055</v>
       </c>
       <c r="E9" t="n">
-        <v>341129.6465493224</v>
+        <v>307873.4841197442</v>
       </c>
       <c r="F9" t="n">
-        <v>69.68459967850939</v>
+        <v>62.89116384204486</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19662.5278108136</v>
+        <v>21247.56860795812</v>
       </c>
       <c r="D10" t="n">
-        <v>49.52999877929688</v>
+        <v>49.91500091552734</v>
       </c>
       <c r="E10" t="n">
-        <v>973884.9784674885</v>
+        <v>1060572.40651896</v>
       </c>
       <c r="F10" t="n">
-        <v>187.0365578846381</v>
+        <v>203.6850518167793</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1100,16 +1100,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16502.46934152341</v>
+        <v>15787.5483185947</v>
       </c>
       <c r="D11" t="n">
-        <v>163.7700042724609</v>
+        <v>163.6900024414062</v>
       </c>
       <c r="E11" t="n">
-        <v>2702609.474567445</v>
+        <v>2584263.822814585</v>
       </c>
       <c r="F11" t="n">
-        <v>431.5283574136585</v>
+        <v>412.6319888526277</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6739.401903224707</v>
+        <v>7131.185015196284</v>
       </c>
       <c r="D12" t="n">
-        <v>135.9900054931641</v>
+        <v>136.5599975585938</v>
       </c>
       <c r="E12" t="n">
-        <v>916491.3018401682</v>
+        <v>973834.6082650848</v>
       </c>
       <c r="F12" t="n">
-        <v>144.0568522971432</v>
+        <v>153.0702452309308</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3267.606407570322</v>
+        <v>4796.472816393295</v>
       </c>
       <c r="D13" t="n">
-        <v>81.88999938964844</v>
+        <v>82.33000183105469</v>
       </c>
       <c r="E13" t="n">
-        <v>267584.286721545</v>
+        <v>394893.615756264</v>
       </c>
       <c r="F13" t="n">
-        <v>45.61964229029604</v>
+        <v>67.32422786943819</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51606.02126301121</v>
+        <v>51793.48121020371</v>
       </c>
       <c r="D14" t="n">
-        <v>46.34000015258789</v>
+        <v>46.41500091552734</v>
       </c>
       <c r="E14" t="n">
-        <v>2391423.033202393</v>
+        <v>2403994.477789953</v>
       </c>
       <c r="F14" t="n">
-        <v>517.9176605697419</v>
+        <v>520.6402960384036</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
